--- a/artfynd/A 6816-2026 artfynd.xlsx
+++ b/artfynd/A 6816-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112925003</v>
       </c>
       <c r="B2" t="n">
-        <v>86245</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565333</v>
+        <v>565332</v>
       </c>
       <c r="R2" t="n">
         <v>6744394</v>
@@ -785,12 +780,7 @@
         <v>112925004</v>
       </c>
       <c r="B3" t="n">
-        <v>81766</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,7 +812,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565333</v>
+        <v>565332</v>
       </c>
       <c r="R3" t="n">
         <v>6744394</v>
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114567010</v>
+        <v>112925002</v>
       </c>
       <c r="B4" t="n">
-        <v>96616</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,37 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Horndal-Fallviken, Dlr</t>
+          <t>Brattbackmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565389</v>
+        <v>565439</v>
       </c>
       <c r="R4" t="n">
-        <v>6744130</v>
+        <v>6744269</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,12 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,19 +960,228 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>björkhögstubbe vid dike</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112925000</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brattbackmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565386</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6744417</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114567010</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Horndal-Fallviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565389</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6744130</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Mårten Nilsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Mårten Nilsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6816-2026 artfynd.xlsx
+++ b/artfynd/A 6816-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112925003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112925004</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112925002</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112925000</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>